--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0088.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0088.xlsx
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Qua nhiều thế hệ, sứ mệnh của gia tộc Fisalia là cộng hưởng với sức mạnh còn sót lại của Người Bảo Hộ và tìm ra Cộng Hưởng Giả của Ngài – Trinh Nữ Được Ban Phước.</t>
+          <t>Qua nhiều thế hệ, sứ mệnh của gia tộc Fisalia là cộng hưởng với sức mạnh còn sót lại của Người Bảo Hộ và tìm ra Resonator của Ngài – Trinh Nữ Được Ban Phước.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Tôi sẽ suy nghĩ về chuyện đó.</t>
+          <t>Ta sẽ suy nghĩ về chuyện này.</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Cậu sợ cái gì thế? Ta biết rõ cậu đã làm gì trước khi đến Lahai-Roi...</t>
+          <t>Cậu sợ cái gì thế? Tao biết rõ cậu đã làm gì trước khi đến Lahai-Roi...</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Ôi, khoan, khoan đã. Ta cũng biết ngươi từng làm gì, nhưng biết trong đầu là một chuyện… nói ra miệng lại là chuyện khác. Thôi đi.</t>
+          <t>Ôi, khoan, khoan đã. Tao cũng biết mày từng làm gì, nhưng biết trong đầu là một chuyện… nói ra miệng lại là chuyện khác. Thôi đi.</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Báo trước cho ta một tiếng trước khi cậu đi... Ta sẽ tiễn cậu đến Starward Riseway.</t>
+          <t>Báo trước cho tao một tiếng trước khi cậu đi... Tao sẽ tiễn cậu đến Starward Riseway.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Ta biết ngươi nhớ chị gái mình, nhưng Soliskin trở về hôm qua vẫn đang đợi ngươi đấy.</t>
+          <t>Tao biết mày nhớ chị gái mình, nhưng Soliskin trở về hôm qua vẫn đang đợi mày đấy.</t>
         </is>
       </c>
     </row>
